--- a/WorkBot/refactor-experimental/data/orders/Sysco/Sysco_Triphammer_20260306.xlsx
+++ b/WorkBot/refactor-experimental/data/orders/Sysco/Sysco_Triphammer_20260306.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -758,6 +758,615 @@
         <v>32.91</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>9035601</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>American Cheese (Sliced)</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>43.95</v>
+      </c>
+      <c r="E17" t="n">
+        <v>87.90000000000001</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>8337503</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Avocado - Hand Scooped</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>9</v>
+      </c>
+      <c r="D18" t="n">
+        <v>53.94</v>
+      </c>
+      <c r="E18" t="n">
+        <v>485.46</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>1956804</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Asiago (Shredded)</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>57.89</v>
+      </c>
+      <c r="E19" t="n">
+        <v>57.89</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>6725030</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Bacon Thick Cut (Smoked)</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" t="n">
+        <v>65.59</v>
+      </c>
+      <c r="E20" t="n">
+        <v>196.77</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>7613284</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Can - Coconut Milk</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>57.45</v>
+      </c>
+      <c r="E21" t="n">
+        <v>114.9</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>1243724</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Cauliflower - Fresh</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>55.85</v>
+      </c>
+      <c r="E22" t="n">
+        <v>55.85</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1735372</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Cucumber (English)</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" t="n">
+        <v>16.12</v>
+      </c>
+      <c r="E23" t="n">
+        <v>64.48</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2416691</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Lettuce - Romaine Hearts</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" t="n">
+        <v>44.78</v>
+      </c>
+      <c r="E24" t="n">
+        <v>134.34</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>1094663</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Onion - Red Jumbo Fresh</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="E25" t="n">
+        <v>17.95</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>4615704</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Pepper - Red Bell Fresh</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>53.99</v>
+      </c>
+      <c r="E26" t="n">
+        <v>53.99</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>7152564</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Sweet Potato</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>30.95</v>
+      </c>
+      <c r="E27" t="n">
+        <v>30.95</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>1592336</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Ham (Unsliced)</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>4</v>
+      </c>
+      <c r="D28" t="n">
+        <v>66.95999999999999</v>
+      </c>
+      <c r="E28" t="n">
+        <v>267.84</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>7199860</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Hard Boiled Egg</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>3</v>
+      </c>
+      <c r="D29" t="n">
+        <v>34.29</v>
+      </c>
+      <c r="E29" t="n">
+        <v>102.87</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>0017354</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Hash Brown</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>4</v>
+      </c>
+      <c r="D30" t="n">
+        <v>23.45</v>
+      </c>
+      <c r="E30" t="n">
+        <v>93.8</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>5833462</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Jalapenos (Sliced)</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" t="n">
+        <v>27</v>
+      </c>
+      <c r="E31" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2366607</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Liquid Egg</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>44.65</v>
+      </c>
+      <c r="E32" t="n">
+        <v>44.65</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>7128077</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Olive - Kalamata (Pitted)</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>59.99</v>
+      </c>
+      <c r="E33" t="n">
+        <v>59.99</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>7256054</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Cheddar - Orange (Unsliced)</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>38</v>
+      </c>
+      <c r="E34" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>7133036</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Chicken - Diced White &amp; Dark</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>10</v>
+      </c>
+      <c r="D35" t="n">
+        <v>45.49</v>
+      </c>
+      <c r="E35" t="n">
+        <v>454.9</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>5042650</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Cornichons</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>202.99</v>
+      </c>
+      <c r="E36" t="n">
+        <v>202.99</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>4438911</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Grain Blend 5 Way</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="n">
+        <v>77.84999999999999</v>
+      </c>
+      <c r="E37" t="n">
+        <v>77.84999999999999</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>4828802</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Heavy Cream</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>1</v>
+      </c>
+      <c r="D38" t="n">
+        <v>45.49</v>
+      </c>
+      <c r="E38" t="n">
+        <v>45.49</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>7524051</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Hot Sauce - Franks Gal</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="E39" t="n">
+        <v>60.4</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>4019139</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Juice - Vegetable V-8 Bulk</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="n">
+        <v>35.68</v>
+      </c>
+      <c r="E40" t="n">
+        <v>35.68</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>4171902</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Manchego Cheese</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" t="n">
+        <v>84.90000000000001</v>
+      </c>
+      <c r="E41" t="n">
+        <v>84.90000000000001</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>4579587</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Mayo</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>6</v>
+      </c>
+      <c r="D42" t="n">
+        <v>45.09</v>
+      </c>
+      <c r="E42" t="n">
+        <v>270.54</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>7836562</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Meat Ball All Beef</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>3</v>
+      </c>
+      <c r="D43" t="n">
+        <v>65.84999999999999</v>
+      </c>
+      <c r="E43" t="n">
+        <v>197.55</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>7226918</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Mozz (Sliced)</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>2</v>
+      </c>
+      <c r="D44" t="n">
+        <v>26.95</v>
+      </c>
+      <c r="E44" t="n">
+        <v>53.9</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>7213975</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Potsticker - Pork &amp; Veg</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>2</v>
+      </c>
+      <c r="D45" t="n">
+        <v>42.28</v>
+      </c>
+      <c r="E45" t="n">
+        <v>84.56</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
